--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009280716500011318</v>
+        <v>0.009422876293346941</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009280716500011318</v>
+        <v>0.009422876293346941</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009107947307379016</v>
+        <v>0.009259153319806004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009107947307379016</v>
+        <v>0.009259153319806004</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009130420183179775</v>
+        <v>0.009276939377030608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009130420183179775</v>
+        <v>0.009276939377030608</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.009133527802268901</v>
+        <v>0.009266575452569882</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009133527802268901</v>
+        <v>0.009266575452569882</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009047050142815193</v>
+        <v>0.009160855437140122</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009047050142815193</v>
+        <v>0.009160855437140122</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.008980661005707916</v>
+        <v>0.009072844607035504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008980661005707916</v>
+        <v>0.009072844607035504</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008858550070657827</v>
+        <v>0.008928130923288639</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008858550070657827</v>
+        <v>0.008928130923288639</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008725755902897748</v>
+        <v>0.008771601649093385</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008725755902897748</v>
+        <v>0.008771601649093385</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008585029978002909</v>
+        <v>0.008607700394001097</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008585029978002909</v>
+        <v>0.008607700394001097</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008442848028808337</v>
+        <v>0.008444121067561544</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008442848028808337</v>
+        <v>0.008444121067561544</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008305891405602506</v>
+        <v>0.008288163214814142</v>
       </c>
       <c r="C12" t="n">
-        <v>0.008305891405602506</v>
+        <v>0.008288163214814142</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008180865325708057</v>
+        <v>0.008147174782538538</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008180865325708057</v>
+        <v>0.008147174782538538</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008071953605183601</v>
+        <v>0.008025580637398578</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008071953605183601</v>
+        <v>0.008025580637398578</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007980897177515361</v>
+        <v>0.007925124995650191</v>
       </c>
       <c r="C15" t="n">
-        <v>0.007980897177515361</v>
+        <v>0.007925124995650191</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.007908548116941401</v>
+        <v>0.007846554743072947</v>
       </c>
       <c r="C16" t="n">
-        <v>0.007908548116941401</v>
+        <v>0.007846554743072947</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.007856211273905893</v>
+        <v>0.007791051721135923</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007856211273905893</v>
+        <v>0.007791051721135923</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00782639048013933</v>
+        <v>0.007761025517239584</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00782639048013933</v>
+        <v>0.007761025517239584</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.007822201728336121</v>
+        <v>0.007759492711753982</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007822201728336121</v>
+        <v>0.007759492711753982</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.007846735594689286</v>
+        <v>0.007789436540866172</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007846735594689286</v>
+        <v>0.007789436540866172</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007902520441883895</v>
+        <v>0.007853241107777706</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007902520441883895</v>
+        <v>0.007853241107777706</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.007990935866549309</v>
+        <v>0.007952048355799744</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007990935866549309</v>
+        <v>0.007952048355799744</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.008114582669924444</v>
+        <v>0.008088445829466702</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008114582669924444</v>
+        <v>0.008088445829466702</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.008254356036374304</v>
+        <v>0.008242820690491901</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008254356036374304</v>
+        <v>0.008242820690491901</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.008445565750982129</v>
+        <v>0.008450608527386046</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008445565750982129</v>
+        <v>0.008450608527386046</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.008677062460226021</v>
+        <v>0.008700704224760216</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008677062460226021</v>
+        <v>0.008700704224760216</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.008951306541103689</v>
+        <v>0.008995294269465767</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008951306541103689</v>
+        <v>0.008995294269465767</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.009270104122534862</v>
+        <v>0.009336250830159419</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009270104122534862</v>
+        <v>0.009336250830159419</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.009634280961979817</v>
+        <v>0.009724228040800359</v>
       </c>
       <c r="C29" t="n">
-        <v>0.009634280961979817</v>
+        <v>0.009724228040800359</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01004434143051447</v>
+        <v>0.01015966439371512</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01004434143051447</v>
+        <v>0.01015966439371512</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01050130053711329</v>
+        <v>0.0106435100829528</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01050130053711329</v>
+        <v>0.0106435100829528</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
